--- a/event_registration_forms/040_photography_photo_package_order_form_2--event_registration_forms.xlsx
+++ b/event_registration_forms/040_photography_photo_package_order_form_2--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>event_date_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Event Date 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>event_time</t>
+          <t>event_time_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Event Time</t>
+          <t>Event Time 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>event_location</t>
+          <t>event_location_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Event Location</t>
+          <t>Event Location 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>photographer_name</t>
+          <t>photographer_name_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
